--- a/dados/excel/folha_mensal_ipca.xlsx
+++ b/dados/excel/folha_mensal_ipca.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Série temporal" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$F$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$F$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -127,22 +127,22 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -661,17 +661,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>﻿ano</t>
+          <t>ano</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Número decimal (#,##0,00)</t>
+          <t>Número inteiro (#,##0)</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -783,13 +783,13 @@
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>﻿ano</t>
+          <t>ano</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
@@ -822,1124 +822,1144 @@
       <c r="A2" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="9" t="n">
         <v>70274692.34</v>
       </c>
-      <c r="D2" s="8" t="n">
-        <v>100.54</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>0.994629</v>
-      </c>
-      <c r="F2" s="10" t="n">
-        <v>69897247.2050925</v>
+      <c r="D2" s="10" t="n">
+        <v>101.2739</v>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>0.987421</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>69390695.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="12" t="n">
         <v>59377915.16</v>
       </c>
-      <c r="D3" s="11" t="n">
-        <v>101.5555</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>0.9846837000000001</v>
-      </c>
-      <c r="F3" s="13" t="n">
-        <v>58468465.08115654</v>
+      <c r="D3" s="13" t="n">
+        <v>102.2968</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>0.977548</v>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>58044738.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="9" t="n">
         <v>68865322.84</v>
       </c>
-      <c r="D4" s="8" t="n">
-        <v>103.2007</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>0.9689861</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>66729542.17696569</v>
+      <c r="D4" s="10" t="n">
+        <v>103.954</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0.961964</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>66245946.77</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="12" t="n">
         <v>72460130.02</v>
       </c>
-      <c r="D5" s="11" t="n">
-        <v>104.2946</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>0.9588226</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>69476410.4974045</v>
+      <c r="D5" s="13" t="n">
+        <v>105.0559</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>0.951874</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>68972908.27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="9" t="n">
         <v>75198274.98</v>
       </c>
-      <c r="D6" s="8" t="n">
-        <v>104.7848</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>0.9543372</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>71764512.5669551</v>
+      <c r="D6" s="10" t="n">
+        <v>105.5497</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.947421</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>71244428.23999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="12" t="n">
         <v>74859337.17</v>
       </c>
-      <c r="D7" s="11" t="n">
-        <v>105.4868</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>0.9479857</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>70965582.19943963</v>
+      <c r="D7" s="13" t="n">
+        <v>106.2569</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>0.941116</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>70451287.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="9" t="n">
         <v>75946079.45</v>
       </c>
-      <c r="D8" s="8" t="n">
-        <v>104.7695</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0.9544762</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>72488721.66302824</v>
+      <c r="D8" s="10" t="n">
+        <v>105.5343</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.947559</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>71963388.92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="12" t="n">
         <v>73121820.31999999</v>
       </c>
-      <c r="D9" s="11" t="n">
-        <v>104.3923</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>0.9579247</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>70045196.38372432</v>
+      <c r="D9" s="13" t="n">
+        <v>105.1544</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>0.950983</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>69537572.11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="9" t="n">
         <v>75871210.59</v>
       </c>
-      <c r="D10" s="8" t="n">
-        <v>104.0896</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>0.9607107</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>72890287.01262622</v>
+      <c r="D10" s="10" t="n">
+        <v>104.8495</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0.953748</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>72362044.09</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="12" t="n">
         <v>78465962.79000001</v>
       </c>
-      <c r="D11" s="11" t="n">
-        <v>104.7037</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>0.9550758</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>74940941.76723488</v>
+      <c r="D11" s="13" t="n">
+        <v>105.4681</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>0.9481540000000001</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>74397837.55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="9" t="n">
         <v>103275264.46</v>
       </c>
-      <c r="D12" s="8" t="n">
-        <v>105.133</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>0.951176</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>98232950.17950724</v>
+      <c r="D12" s="10" t="n">
+        <v>105.9005</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0.944283</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>97521046.54000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="12" t="n">
         <v>141153690.4</v>
       </c>
-      <c r="D13" s="11" t="n">
-        <v>105.7848</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>0.945315</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>133434703.6732325</v>
+      <c r="D13" s="13" t="n">
+        <v>106.5571</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>0.938464</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>132467689.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="9" t="n">
         <v>81143980.59</v>
       </c>
-      <c r="D14" s="8" t="n">
-        <v>106.3455</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>0.9403313</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>76302221.86400248</v>
+      <c r="D14" s="10" t="n">
+        <v>107.1218</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0.933517</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>75749252.31999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="12" t="n">
         <v>83152573.62</v>
       </c>
-      <c r="D15" s="11" t="n">
-        <v>107.2388</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>0.9324983</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>77539631.78054544</v>
+      <c r="D15" s="13" t="n">
+        <v>108.0216</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>0.92574</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>76977694.61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="9" t="n">
         <v>91939165.01000001</v>
       </c>
-      <c r="D16" s="8" t="n">
-        <v>108.0002</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>0.9259242</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>85128699.3629846</v>
+      <c r="D16" s="10" t="n">
+        <v>108.7886</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0.919214</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>84511763.48999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="12" t="n">
         <v>80393809.94</v>
       </c>
-      <c r="D17" s="11" t="n">
-        <v>108.659</v>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>0.9203103</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>73987253.26620676</v>
+      <c r="D17" s="13" t="n">
+        <v>109.4522</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>0.913641</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>73451060.52</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="9" t="n">
         <v>80588758.53</v>
       </c>
-      <c r="D18" s="8" t="n">
-        <v>108.9089</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>0.9181985</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>73996474.57469358</v>
+      <c r="D18" s="10" t="n">
+        <v>109.704</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0.911544</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>73460215.01000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="12" t="n">
         <v>83834223.13</v>
       </c>
-      <c r="D19" s="11" t="n">
-        <v>108.8218</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>0.9189336</v>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>77038085.66505849</v>
+      <c r="D19" s="13" t="n">
+        <v>109.6162</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>0.912274</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>76479783.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C20" s="10" t="n">
+      <c r="C20" s="9" t="n">
         <v>87293434.09</v>
       </c>
-      <c r="D20" s="8" t="n">
-        <v>108.9524</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>0.9178322</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>80120726.02401838</v>
+      <c r="D20" s="10" t="n">
+        <v>109.7477</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0.911181</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>79540083.42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="12" t="n">
         <v>89727793.84999999</v>
       </c>
-      <c r="D21" s="11" t="n">
-        <v>109.203</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>0.915726</v>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>82166077.85719857</v>
+      <c r="D21" s="13" t="n">
+        <v>110.0001</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>0.90909</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>81570612.39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C22" s="9" t="n">
         <v>89621692.59</v>
       </c>
-      <c r="D22" s="8" t="n">
-        <v>109.4869</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>0.9133513</v>
-      </c>
-      <c r="F22" s="10" t="n">
-        <v>81856092.32987075</v>
+      <c r="D22" s="10" t="n">
+        <v>110.2861</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0.906732</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>81262873.34999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B23" s="12" t="n">
+      <c r="B23" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="12" t="n">
         <v>89485511.73999999</v>
       </c>
-      <c r="D23" s="11" t="n">
-        <v>109.7497</v>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>0.9111645</v>
-      </c>
-      <c r="F23" s="13" t="n">
-        <v>81536024.90930744</v>
+      <c r="D23" s="13" t="n">
+        <v>110.5508</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>0.9045609999999999</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>80945125.48999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C24" s="9" t="n">
         <v>120240059.83</v>
       </c>
-      <c r="D24" s="8" t="n">
-        <v>110.057</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>0.9086204</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>109252571.2933073</v>
+      <c r="D24" s="10" t="n">
+        <v>110.8604</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0.9020359999999999</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>108460807.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="12" t="n">
         <v>169348904.26</v>
       </c>
-      <c r="D25" s="11" t="n">
-        <v>110.6733</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>0.9035605</v>
-      </c>
-      <c r="F25" s="13" t="n">
-        <v>153016974.1218598</v>
+      <c r="D25" s="13" t="n">
+        <v>111.4812</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>0.897012</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>151908045.39</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B26" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="10" t="n">
+      <c r="C26" s="9" t="n">
         <v>96436581.84999999</v>
       </c>
-      <c r="D26" s="8" t="n">
-        <v>111.1381</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>0.8997814</v>
-      </c>
-      <c r="F26" s="10" t="n">
-        <v>86771840.69042978</v>
+      <c r="D26" s="10" t="n">
+        <v>111.9494</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0.893261</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>86142996.81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B27" s="12" t="n">
+      <c r="B27" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C27" s="13" t="n">
+      <c r="C27" s="12" t="n">
         <v>87603467.53</v>
       </c>
-      <c r="D27" s="11" t="n">
-        <v>112.0606</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>0.8923747</v>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>78175115.4405544</v>
+      <c r="D27" s="13" t="n">
+        <v>112.8786</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>0.885908</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>77608572.86</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B28" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C28" s="9" t="n">
         <v>109326020.21</v>
       </c>
-      <c r="D28" s="8" t="n">
-        <v>112.2399</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>0.8909492</v>
-      </c>
-      <c r="F28" s="10" t="n">
-        <v>97403924.94314604</v>
+      <c r="D28" s="10" t="n">
+        <v>113.0592</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0.8844919999999999</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>96698029.33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C29" s="13" t="n">
+      <c r="C29" s="12" t="n">
         <v>101013090.35</v>
       </c>
-      <c r="D29" s="11" t="n">
-        <v>112.6664</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>0.8875764</v>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>89656831.179405</v>
+      <c r="D29" s="13" t="n">
+        <v>113.4888</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>0.881144</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>89007079.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B30" s="9" t="n">
+      <c r="B30" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C30" s="10" t="n">
+      <c r="C30" s="9" t="n">
         <v>98870785.13</v>
       </c>
-      <c r="D30" s="8" t="n">
-        <v>113.1846</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>0.8835122</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>87353545.39854892</v>
+      <c r="D30" s="10" t="n">
+        <v>114.0109</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.877109</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>86720485.84999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B31" s="12" t="n">
+      <c r="B31" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C31" s="13" t="n">
+      <c r="C31" s="12" t="n">
         <v>97820809.59999999</v>
       </c>
-      <c r="D31" s="11" t="n">
-        <v>113.4223</v>
-      </c>
-      <c r="E31" s="11" t="n">
-        <v>0.8816607</v>
-      </c>
-      <c r="F31" s="13" t="n">
-        <v>86244765.1957376</v>
+      <c r="D31" s="13" t="n">
+        <v>114.2503</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>0.875271</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>85619741.09</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B32" s="9" t="n">
+      <c r="B32" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C32" s="10" t="n">
+      <c r="C32" s="9" t="n">
         <v>99864776.48</v>
       </c>
-      <c r="D32" s="8" t="n">
-        <v>113.8533</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>0.8783231</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>87713539.05366367</v>
+      <c r="D32" s="10" t="n">
+        <v>114.6844</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0.871958</v>
+      </c>
+      <c r="F32" s="9" t="n">
+        <v>87077870.59999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C33" s="13" t="n">
+      <c r="C33" s="12" t="n">
         <v>95317817.08</v>
       </c>
-      <c r="D33" s="11" t="n">
-        <v>113.8305</v>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>0.8784988</v>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>83736586.94103114</v>
+      <c r="D33" s="13" t="n">
+        <v>114.6615</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>0.872132</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>83129739.84</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B34" s="9" t="n">
+      <c r="B34" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C34" s="10" t="n">
+      <c r="C34" s="9" t="n">
         <v>97837400.11</v>
       </c>
-      <c r="D34" s="8" t="n">
-        <v>114.3314</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>0.8746503</v>
-      </c>
-      <c r="F34" s="10" t="n">
-        <v>85573514.12128542</v>
+      <c r="D34" s="10" t="n">
+        <v>115.166</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0.868312</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>84953354.63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B35" s="12" t="n">
+      <c r="B35" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C35" s="13" t="n">
+      <c r="C35" s="12" t="n">
         <v>98516206.09999999</v>
       </c>
-      <c r="D35" s="11" t="n">
-        <v>114.9717</v>
-      </c>
-      <c r="E35" s="11" t="n">
-        <v>0.8697796</v>
-      </c>
-      <c r="F35" s="13" t="n">
-        <v>85687382.66035862</v>
+      <c r="D35" s="13" t="n">
+        <v>115.811</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>0.863476</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>85066397.95999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B36" s="9" t="n">
+      <c r="B36" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C36" s="10" t="n">
+      <c r="C36" s="9" t="n">
         <v>164842333.46</v>
       </c>
-      <c r="D36" s="8" t="n">
-        <v>115.42</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>0.8664006</v>
-      </c>
-      <c r="F36" s="10" t="n">
-        <v>142819496.673986</v>
+      <c r="D36" s="10" t="n">
+        <v>116.2626</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0.8601220000000001</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>141784470.04</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B37" s="12" t="n">
+      <c r="B37" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C37" s="13" t="n">
+      <c r="C37" s="12" t="n">
         <v>174687312.44</v>
       </c>
-      <c r="D37" s="11" t="n">
-        <v>116.0202</v>
-      </c>
-      <c r="E37" s="11" t="n">
-        <v>0.8619186</v>
-      </c>
-      <c r="F37" s="13" t="n">
-        <v>150566247.8837641</v>
+      <c r="D37" s="13" t="n">
+        <v>116.8672</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>0.855672</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>149475079.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B38" s="9" t="n">
+      <c r="B38" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="10" t="n">
+      <c r="C38" s="9" t="n">
         <v>104916189.43</v>
       </c>
-      <c r="D38" s="8" t="n">
-        <v>116.2059</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>0.8605418</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>90284761.95877725</v>
+      <c r="D38" s="10" t="n">
+        <v>117.0542</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0.854305</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>89630459.59999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="13" t="n">
+      <c r="C39" s="12" t="n">
         <v>97394039.81999999</v>
       </c>
-      <c r="D39" s="11" t="n">
-        <v>117.7282</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>0.8494144</v>
-      </c>
-      <c r="F39" s="13" t="n">
-        <v>82727902.59520073</v>
+      <c r="D39" s="13" t="n">
+        <v>118.5876</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>0.843259</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>82128365.53</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B40" s="9" t="n">
+      <c r="B40" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C40" s="10" t="n">
+      <c r="C40" s="9" t="n">
         <v>122414115.01</v>
       </c>
-      <c r="D40" s="8" t="n">
-        <v>118.3874</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>0.8446842</v>
-      </c>
-      <c r="F40" s="10" t="n">
-        <v>103401268.3410425</v>
+      <c r="D40" s="10" t="n">
+        <v>119.2517</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0.8385629999999999</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>102651909.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B41" s="12" t="n">
+      <c r="B41" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C41" s="13" t="n">
+      <c r="C41" s="12" t="n">
         <v>107027107.06</v>
       </c>
-      <c r="D41" s="11" t="n">
-        <v>118.8965</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>0.8410676</v>
-      </c>
-      <c r="F41" s="13" t="n">
-        <v>90017032.65840665</v>
+      <c r="D41" s="13" t="n">
+        <v>119.7645</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>0.834972</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>89364670.56</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B42" s="9" t="n">
+      <c r="B42" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C42" s="10" t="n">
+      <c r="C42" s="9" t="n">
         <v>108027237.48</v>
       </c>
-      <c r="D42" s="8" t="n">
-        <v>119.2056</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>0.8388865</v>
-      </c>
-      <c r="F42" s="10" t="n">
-        <v>90622591.21877363</v>
+      <c r="D42" s="10" t="n">
+        <v>120.0758</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0.832807</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>89965840.58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C43" s="13" t="n">
+      <c r="C43" s="12" t="n">
         <v>112514239.75</v>
       </c>
-      <c r="D43" s="11" t="n">
-        <v>119.4917</v>
-      </c>
-      <c r="E43" s="11" t="n">
-        <v>0.836878</v>
-      </c>
-      <c r="F43" s="13" t="n">
-        <v>94160691.19236369</v>
+      <c r="D43" s="13" t="n">
+        <v>120.364</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>0.830813</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>93478299.61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B44" s="9" t="n">
+      <c r="B44" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C44" s="10" t="n">
+      <c r="C44" s="9" t="n">
         <v>112522782.32</v>
       </c>
-      <c r="D44" s="8" t="n">
-        <v>119.8024</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>0.8347078</v>
-      </c>
-      <c r="F44" s="10" t="n">
-        <v>93923638.82027118</v>
+      <c r="D44" s="10" t="n">
+        <v>120.677</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0.828659</v>
+      </c>
+      <c r="F44" s="9" t="n">
+        <v>93242965.17</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B45" s="12" t="n">
+      <c r="B45" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C45" s="13" t="n">
+      <c r="C45" s="12" t="n">
         <v>110463399.24</v>
       </c>
-      <c r="D45" s="11" t="n">
-        <v>119.6706</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>0.8356269</v>
-      </c>
-      <c r="F45" s="13" t="n">
-        <v>92306192.60834324</v>
+      <c r="D45" s="13" t="n">
+        <v>120.5442</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>0.8295709999999999</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>91637240.75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B46" s="9" t="n">
+      <c r="B46" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C46" s="10" t="n">
+      <c r="C46" s="9" t="n">
         <v>111734035.32</v>
       </c>
-      <c r="D46" s="8" t="n">
-        <v>120.245</v>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>0.8316351</v>
-      </c>
-      <c r="F46" s="10" t="n">
-        <v>92921945.01532793</v>
+      <c r="D46" s="10" t="n">
+        <v>121.1228</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0.825608</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>92248530.73999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B47" s="12" t="n">
+      <c r="B47" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C47" s="13" t="n">
+      <c r="C47" s="12" t="n">
         <v>110279554.48</v>
       </c>
-      <c r="D47" s="11" t="n">
-        <v>120.3533</v>
-      </c>
-      <c r="E47" s="11" t="n">
-        <v>0.8308873</v>
-      </c>
-      <c r="F47" s="13" t="n">
-        <v>91629880.81186505</v>
+      <c r="D47" s="13" t="n">
+        <v>121.2318</v>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>0.824866</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>90965830.25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B48" s="9" t="n">
+      <c r="B48" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C48" s="10" t="n">
+      <c r="C48" s="9" t="n">
         <v>147355080.14</v>
       </c>
-      <c r="D48" s="8" t="n">
-        <v>120.5699</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>0.8293944</v>
-      </c>
-      <c r="F48" s="10" t="n">
-        <v>122215476.2133544</v>
+      <c r="D48" s="10" t="n">
+        <v>121.4501</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0.823384</v>
+      </c>
+      <c r="F48" s="9" t="n">
+        <v>121329768.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B49" s="12" t="n">
+      <c r="B49" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C49" s="13" t="n">
+      <c r="C49" s="12" t="n">
         <v>195618641.99</v>
       </c>
-      <c r="D49" s="11" t="n">
-        <v>120.9678</v>
-      </c>
-      <c r="E49" s="11" t="n">
-        <v>0.8266664</v>
-      </c>
-      <c r="F49" s="13" t="n">
-        <v>161711355.9842655</v>
+      <c r="D49" s="13" t="n">
+        <v>121.8508</v>
+      </c>
+      <c r="E49" s="13" t="n">
+        <v>0.820675</v>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>160539418.23</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B50" s="9" t="n">
+      <c r="B50" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C50" s="10" t="n">
+      <c r="C50" s="9" t="n">
         <v>119601635.45</v>
       </c>
-      <c r="D50" s="8" t="n">
-        <v>121.367</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>0.8239474</v>
-      </c>
-      <c r="F50" s="10" t="n">
-        <v>98545451.85373095</v>
+      <c r="D50" s="10" t="n">
+        <v>122.253</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0.817976</v>
+      </c>
+      <c r="F50" s="9" t="n">
+        <v>97831283.48</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B51" s="12" t="n">
+      <c r="B51" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C51" s="13" t="n">
+      <c r="C51" s="12" t="n">
         <v>103607784.27</v>
       </c>
-      <c r="D51" s="11" t="n">
-        <v>122.2165</v>
-      </c>
-      <c r="E51" s="11" t="n">
-        <v>0.8182198000000001</v>
-      </c>
-      <c r="F51" s="13" t="n">
-        <v>84773942.78845307</v>
+      <c r="D51" s="13" t="n">
+        <v>123.1087</v>
+      </c>
+      <c r="E51" s="13" t="n">
+        <v>0.81229</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>84159577.87</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B52" s="9" t="n">
+      <c r="B52" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C52" s="10" t="n">
+      <c r="C52" s="9" t="n">
         <v>130341240.2</v>
       </c>
-      <c r="D52" s="8" t="n">
-        <v>123.2921</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>0.8110823</v>
-      </c>
-      <c r="F52" s="10" t="n">
-        <v>105717472.5784436</v>
+      <c r="D52" s="10" t="n">
+        <v>124.1921</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0.805204</v>
+      </c>
+      <c r="F52" s="9" t="n">
+        <v>104951327.88</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B53" s="12" t="n">
+      <c r="B53" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C53" s="13" t="n">
+      <c r="C53" s="12" t="n">
         <v>117938726.44</v>
       </c>
-      <c r="D53" s="11" t="n">
-        <v>124.1181</v>
-      </c>
-      <c r="E53" s="11" t="n">
-        <v>0.8056842</v>
-      </c>
-      <c r="F53" s="13" t="n">
-        <v>95021370.04220915</v>
+      <c r="D53" s="13" t="n">
+        <v>125.0242</v>
+      </c>
+      <c r="E53" s="13" t="n">
+        <v>0.799845</v>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>94332741.03</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B54" s="9" t="n">
+      <c r="B54" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C54" s="10" t="n">
+      <c r="C54" s="9" t="n">
         <v>120069417.43</v>
       </c>
-      <c r="D54" s="8" t="n">
-        <v>124.838</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>0.8010382</v>
-      </c>
-      <c r="F54" s="10" t="n">
-        <v>96180189.04007141</v>
+      <c r="D54" s="10" t="n">
+        <v>125.7493</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0.795233</v>
+      </c>
+      <c r="F54" s="9" t="n">
+        <v>95483161.95999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B55" s="12" t="n">
+      <c r="B55" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C55" s="13" t="n">
+      <c r="C55" s="12" t="n">
         <v>123384176.69</v>
       </c>
-      <c r="D55" s="11" t="n">
-        <v>125.0377</v>
-      </c>
-      <c r="E55" s="11" t="n">
-        <v>0.7997586</v>
-      </c>
-      <c r="F55" s="13" t="n">
-        <v>98677553.71832132</v>
+      <c r="D55" s="13" t="n">
+        <v>125.9505</v>
+      </c>
+      <c r="E55" s="13" t="n">
+        <v>0.793963</v>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>97962427.98999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B56" s="9" t="n">
+      <c r="B56" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C56" s="10" t="n">
+      <c r="C56" s="9" t="n">
         <v>138886330.38</v>
       </c>
-      <c r="D56" s="8" t="n">
-        <v>125.1253</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>0.7991991000000001</v>
-      </c>
-      <c r="F56" s="10" t="n">
-        <v>110997835.627076</v>
+      <c r="D56" s="10" t="n">
+        <v>126.0387</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0.793407</v>
+      </c>
+      <c r="F56" s="9" t="n">
+        <v>110193423.63</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B57" s="12" t="n">
+      <c r="B57" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C57" s="13" t="n">
+      <c r="C57" s="12" t="n">
         <v>124784562.77</v>
       </c>
-      <c r="D57" s="11" t="n">
-        <v>124.7249</v>
-      </c>
-      <c r="E57" s="11" t="n">
-        <v>0.8017648000000001</v>
-      </c>
-      <c r="F57" s="13" t="n">
-        <v>100047868.2764679</v>
+      <c r="D57" s="13" t="n">
+        <v>125.6354</v>
+      </c>
+      <c r="E57" s="13" t="n">
+        <v>0.7959540000000001</v>
+      </c>
+      <c r="F57" s="12" t="n">
+        <v>99322811.75</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>129971219.82</v>
+      </c>
+      <c r="D58" s="10" t="n">
+        <v>126.6656</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0.789481</v>
+      </c>
+      <c r="F58" s="9" t="n">
+        <v>102609753.85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F57"/>
+  <autoFilter ref="A1:F58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1950,7 +1970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1979,7 +1999,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="B4" s="15" t="n">
@@ -1989,7 +2009,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2/2022</t>
         </is>
       </c>
       <c r="B5" s="15" t="n">
@@ -1999,7 +2019,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>3/2022</t>
         </is>
       </c>
       <c r="B6" s="15" t="n">
@@ -2009,7 +2029,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="B7" s="15" t="n">
@@ -2019,7 +2039,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>5/2022</t>
         </is>
       </c>
       <c r="B8" s="15" t="n">
@@ -2029,7 +2049,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="B9" s="15" t="n">
@@ -2039,7 +2059,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>7/2022</t>
         </is>
       </c>
       <c r="B10" s="15" t="n">
@@ -2049,7 +2069,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="B11" s="15" t="n">
@@ -2059,7 +2079,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="B12" s="15" t="n">
@@ -2069,7 +2089,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B13" s="15" t="n">
@@ -2079,7 +2099,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -2089,7 +2109,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -2099,7 +2119,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -2109,7 +2129,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2/2023</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -2119,7 +2139,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>3/2023</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -2129,7 +2149,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -2139,7 +2159,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>5/2023</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -2149,7 +2169,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>6/2023</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -2159,7 +2179,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>7/2023</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -2169,7 +2189,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>8/2023</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -2179,7 +2199,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>9/2023</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -2189,7 +2209,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -2199,7 +2219,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -2209,7 +2229,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -2219,7 +2239,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1/2024</t>
         </is>
       </c>
       <c r="B28" s="15" t="n">
@@ -2229,7 +2249,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="B29" s="15" t="n">
@@ -2239,7 +2259,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>3/2024</t>
         </is>
       </c>
       <c r="B30" s="15" t="n">
@@ -2249,7 +2269,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="B31" s="15" t="n">
@@ -2259,7 +2279,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>5/2024</t>
         </is>
       </c>
       <c r="B32" s="15" t="n">
@@ -2269,7 +2289,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>6/2024</t>
         </is>
       </c>
       <c r="B33" s="15" t="n">
@@ -2279,7 +2299,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>7/2024</t>
         </is>
       </c>
       <c r="B34" s="15" t="n">
@@ -2289,7 +2309,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>8/2024</t>
         </is>
       </c>
       <c r="B35" s="15" t="n">
@@ -2299,7 +2319,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>9/2024</t>
         </is>
       </c>
       <c r="B36" s="15" t="n">
@@ -2309,7 +2329,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B37" s="15" t="n">
@@ -2319,7 +2339,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B38" s="15" t="n">
@@ -2329,7 +2349,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B39" s="15" t="n">
@@ -2339,7 +2359,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>1/2025</t>
         </is>
       </c>
       <c r="B40" s="15" t="n">
@@ -2349,7 +2369,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2/2025</t>
         </is>
       </c>
       <c r="B41" s="15" t="n">
@@ -2359,7 +2379,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>3/2025</t>
         </is>
       </c>
       <c r="B42" s="15" t="n">
@@ -2369,7 +2389,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>4/2025</t>
         </is>
       </c>
       <c r="B43" s="15" t="n">
@@ -2379,7 +2399,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>5/2025</t>
         </is>
       </c>
       <c r="B44" s="15" t="n">
@@ -2389,7 +2409,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>6/2025</t>
         </is>
       </c>
       <c r="B45" s="15" t="n">
@@ -2399,7 +2419,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="B46" s="15" t="n">
@@ -2409,7 +2429,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>8/2025</t>
         </is>
       </c>
       <c r="B47" s="15" t="n">
@@ -2419,7 +2439,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>9/2025</t>
         </is>
       </c>
       <c r="B48" s="15" t="n">
@@ -2429,7 +2449,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B49" s="15" t="n">
@@ -2439,7 +2459,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B50" s="15" t="n">
@@ -2449,7 +2469,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>12/2025</t>
         </is>
       </c>
       <c r="B51" s="15" t="n">
@@ -2459,7 +2479,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1/2026</t>
         </is>
       </c>
       <c r="B52" s="15" t="n">
@@ -2469,7 +2489,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2/2026</t>
         </is>
       </c>
       <c r="B53" s="15" t="n">
@@ -2479,7 +2499,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>3/2026</t>
         </is>
       </c>
       <c r="B54" s="15" t="n">
@@ -2489,7 +2509,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>4/2026</t>
         </is>
       </c>
       <c r="B55" s="15" t="n">
@@ -2499,7 +2519,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="B56" s="15" t="n">
@@ -2509,7 +2529,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>6/2026</t>
         </is>
       </c>
       <c r="B57" s="15" t="n">
@@ -2519,7 +2539,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>7/2026</t>
         </is>
       </c>
       <c r="B58" s="15" t="n">
@@ -2529,11 +2549,21 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>8/2026</t>
         </is>
       </c>
       <c r="B59" s="15" t="n">
         <v>124784562.77</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>9/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="n">
+        <v>129971219.82</v>
       </c>
     </row>
   </sheetData>
